--- a/cbreader2X/authority資料庫更新表_2026R1.xlsx
+++ b/cbreader2X/authority資料庫更新表_2026R1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B014F1-BA32-4BD8-AD26-EBCA7A8A8693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36B146D-1A31-4950-8238-522041BAC12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="79">
   <si>
     <t>CBETA id</t>
   </si>
@@ -228,14 +228,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>YP05</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>YP06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>YP0012</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -345,106 +337,6 @@
   </si>
   <si>
     <t>異部宗輪論語體釋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>維摩詰所說經講記（下）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -606,99 +498,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>維摩詰所說經講記（上）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="微軟正黑體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="微軟正黑體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="微軟正黑體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="微軟正黑體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF4BACC6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <t>YP05..YP06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>維摩詰所說經講記</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -706,7 +510,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -811,13 +615,6 @@
       <color rgb="FFBBBEBF"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4BACC6"/>
-      <name val="微軟正黑體"/>
-      <family val="3"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1512,30 +1309,30 @@
     </row>
     <row r="2" spans="1:13" ht="19.8" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7">
         <v>6</v>
       </c>
       <c r="I2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>30</v>
@@ -1554,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="20.399999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1642,7 +1439,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>30</v>
@@ -1673,7 +1470,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>33</v>
@@ -1704,7 +1501,7 @@
         <v>26</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>21</v>
@@ -1715,7 +1512,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
@@ -1725,17 +1522,17 @@
         <v>18</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>17</v>
@@ -1743,7 +1540,7 @@
     </row>
     <row r="6" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>40</v>
@@ -1755,8 +1552,8 @@
       <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>69</v>
+      <c r="F6" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7">
@@ -1766,7 +1563,7 @@
         <v>23</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>17</v>
@@ -1774,10 +1571,10 @@
     </row>
     <row r="7" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>20</v>
@@ -1787,17 +1584,17 @@
         <v>18</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>17</v>
@@ -1805,10 +1602,10 @@
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>20</v>
@@ -1818,17 +1615,17 @@
         <v>18</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>17</v>
@@ -1836,10 +1633,10 @@
     </row>
     <row r="9" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>20</v>
@@ -1849,17 +1646,17 @@
         <v>18</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>17</v>
@@ -1867,10 +1664,10 @@
     </row>
     <row r="10" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>20</v>
@@ -1890,7 +1687,7 @@
         <v>23</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>17</v>
@@ -1901,7 +1698,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>20</v>
@@ -1911,17 +1708,17 @@
         <v>18</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>17</v>
@@ -1929,10 +1726,10 @@
     </row>
     <row r="12" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>20</v>
@@ -1942,17 +1739,17 @@
         <v>18</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>17</v>
@@ -1960,10 +1757,10 @@
     </row>
     <row r="13" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>20</v>
@@ -1973,17 +1770,17 @@
         <v>18</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>17</v>
@@ -1991,10 +1788,10 @@
     </row>
     <row r="14" spans="1:14" ht="20.399999999999999" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>20</v>
@@ -2008,13 +1805,13 @@
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>17</v>
@@ -2025,7 +1822,7 @@
         <v>64</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>20</v>
@@ -2035,50 +1832,19 @@
         <v>18</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="20.399999999999999" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7">
-        <v>3</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K16" s="7" t="s">
         <v>17</v>
       </c>
     </row>
